--- a/tame_output/ON/bt/strategyON_20240328.xlsx
+++ b/tame_output/ON/bt/strategyON_20240328.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.0%</t>
+          <t>-68.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-539.9%</t>
+          <t>-575.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-45.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-61.3%</t>
+          <t>-62.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.8%</t>
+          <t>-641.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-398.4%</t>
+          <t>-410.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-216.3%</t>
+          <t>-230.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-62.6%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-218.3%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-162.3%</t>
+          <t>-167.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,37 +1318,37 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-143.8%</t>
+          <t>-148.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.4%</t>
+          <t>-143.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-103.4%</t>
+          <t>-89.3%</t>
         </is>
       </c>
     </row>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>-0.01109035984100631</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.121688151287636</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>-0.09286226026875799</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.079062117071773</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>-0.1600713681406357</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.056943790756725</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>-0.1560799153454455</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.056365167994041</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2009865069470839</v>
+        <v>-0.5542283462987061</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.036329422858449</v>
+        <v>2.8950326871178</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4226084405052014</v>
+        <v>-0.7758502798568236</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.947546866034124</v>
+        <v>2.806250130293475</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6306124988582786</v>
+        <v>-0.9838543382099009</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.869237387246818</v>
+        <v>2.727940651506169</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.901012461567164</v>
+        <v>-1.254254300918786</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.756158858501252</v>
+        <v>2.614862122760603</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.240170839155686</v>
+        <v>-1.593412678507308</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.613579806772292</v>
+        <v>2.472283071031643</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.568188060883165</v>
+        <v>-1.921429900234787</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.502711207820068</v>
+        <v>2.36141447207942</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.564851314374194</v>
+        <v>-1.918093153725816</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.512144656832226</v>
+        <v>2.370847921091577</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.931562366040739</v>
+        <v>-2.284804205392361</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.366566628209339</v>
+        <v>2.225269892468691</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.316742756970812</v>
+        <v>-2.669984596322434</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.211037010650174</v>
+        <v>2.069740274909525</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.660425530197474</v>
+        <v>-3.013667369549097</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.075333024814125</v>
+        <v>1.934036289073476</v>
       </c>
       <c r="F1856" t="n">
         <v>0.003417817992306726</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.018075880435823</v>
+        <v>-3.371317719787445</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.928378943375043</v>
+        <v>1.787082207634395</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.3542325322460414</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.02473682065797</v>
+        <v>-3.377978660009592</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.927487493986444</v>
+        <v>1.786190758245795</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.3542325322460414</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.456542613807758</v>
+        <v>-3.80978445315938</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.741098064193933</v>
+        <v>1.599801328453284</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4906500286873084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.782975142675502</v>
+        <v>-4.136216982027124</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.598809827648927</v>
+        <v>1.457513091908277</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.5731182791944566</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.784539293785805</v>
+        <v>-4.137781133137427</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.596764758860771</v>
+        <v>1.455468023120121</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.5731182791944566</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.148165538686118</v>
+        <v>-4.50140737803774</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.457801821134887</v>
+        <v>1.316505085394237</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.6713399160615824</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.145738474157399</v>
+        <v>-4.498980313509022</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.458027161952206</v>
+        <v>1.316730426211556</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.671672697868734</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.554327251338078</v>
+        <v>-4.907569090689701</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.293353195094693</v>
+        <v>1.152056459354044</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.080261475049412</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.967309735479172</v>
+        <v>-5.320551574830795</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.123345633909716</v>
+        <v>0.9820488981690669</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.080261475049412</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.383701609766169</v>
+        <v>-5.736943449117792</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9547829348037946</v>
+        <v>0.8134861990631452</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.080261475049412</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.760378620296014</v>
+        <v>-6.113620459647636</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8143708212605358</v>
+        <v>0.6730740855198865</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.080261475049412</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.774093484621125</v>
+        <v>-6.127335323972748</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.8049844406761864</v>
+        <v>0.663687704935537</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.080261475049412</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.086918283866105</v>
+        <v>-6.440160123217727</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6782594410331955</v>
+        <v>0.5369627052925461</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.080261475049412</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.091731322331442</v>
+        <v>-6.444973161683064</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.680113201576269</v>
+        <v>0.5388164658356196</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.081808109752198</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.525080430441678</v>
+        <v>-6.8783222697933</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5027472537977715</v>
+        <v>0.3614505180571221</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.081808109752198</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.908081819184309</v>
+        <v>-7.261323658535932</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3494445969791347</v>
+        <v>0.2081478612384853</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.081808109752198</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.283067145355586</v>
+        <v>-7.636308984707209</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2020219824820542</v>
+        <v>0.06072524674140478</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.456793435923476</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.642597467859588</v>
+        <v>-7.99583930721121</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0635601567785038</v>
+        <v>-0.07773657896214559</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.456793435923476</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.968997496524601</v>
+        <v>-8.322239335876223</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05908383473032419</v>
+        <v>-0.2003805704709736</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.783193464588488</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.962521349731041</v>
+        <v>-8.315763189082663</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.05345162539113124</v>
+        <v>-0.1947483611317806</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.776717317794929</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.95883042477463</v>
+        <v>-8.312072264126252</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.05197525540856685</v>
+        <v>-0.1932719911492167</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.776717317794929</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.163088600104492</v>
+        <v>-8.516330439456116</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1281653284218693</v>
+        <v>-0.2694620641625196</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.904356262408918</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.323727626592857</v>
+        <v>-8.676969465944481</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1879383845327793</v>
+        <v>-0.3292351202734296</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.019089735411313</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.250257794925409</v>
+        <v>-8.603499634277032</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1431787503723787</v>
+        <v>-0.284475486113029</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.945619903743865</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.425382212311952</v>
+        <v>-8.778624051663575</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1986732965794795</v>
+        <v>-0.3399700323201293</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.120744321130409</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.659834306326442</v>
+        <v>-9.013076145678065</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2996732990868711</v>
+        <v>-0.4409700348275214</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.120744321130409</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.94763815086368</v>
+        <v>-9.300879990215304</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4214670276757428</v>
+        <v>-0.5627637634163931</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.408548165667647</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.177462598027505</v>
+        <v>-9.530704437379129</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5122810167027163</v>
+        <v>-0.6535777524433666</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.571195702737807</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.114393365721165</v>
+        <v>-9.467635205072789</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4843595951510657</v>
+        <v>-0.625656330891716</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.599709265420042</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.062377851752352</v>
+        <v>-9.415619691103975</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4595630538771398</v>
+        <v>-0.6008597896177896</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.599709265420042</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.143669781306556</v>
+        <v>-9.49691162065818</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4935550525975634</v>
+        <v>-0.6348517883382132</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.599709265420042</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.946400375578559</v>
+        <v>-9.299642214930183</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.399593880141492</v>
+        <v>-0.5408906158821423</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.402439859692044</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.74724826834146</v>
+        <v>-9.100490107693084</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.3329841708933352</v>
+        <v>-0.4742809066339855</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.23711733374223</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.52140311562205</v>
+        <v>-8.874644954973673</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.2330670367693628</v>
+        <v>-0.3743637725100126</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.195190658155067</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.235128303299355</v>
+        <v>-8.588370142650978</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.1174179672842257</v>
+        <v>-0.258714703024876</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.195190658155067</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.008332476226022</v>
+        <v>-8.361574315577645</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.02406586229278496</v>
+        <v>-0.1653625980334348</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.127076713533522</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.724423745297273</v>
+        <v>-8.077665584648896</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.0952313343173512</v>
+        <v>-0.04606540142329862</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.127076713533522</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.47743649510432</v>
+        <v>-7.830678334455944</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.1842889720006671</v>
+        <v>0.0429922362600168</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.88008946334057</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.213599627900251</v>
+        <v>-7.566841467251875</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.2799402375693871</v>
+        <v>0.1386435018287369</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.88008946334057</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.946357827031854</v>
+        <v>-7.299599666383478</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.385002397417372</v>
+        <v>0.2437056616767221</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.88008946334057</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.67054866363137</v>
+        <v>-7.023790502982994</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.4950257478041049</v>
+        <v>0.3537290120634546</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.791070155061837</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.401481075864391</v>
+        <v>-6.754722915216014</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.6033212890563902</v>
+        <v>0.4620245533157403</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.522002567294857</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.137421137541595</v>
+        <v>-6.490662976893218</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.6956849482237564</v>
+        <v>0.5543882124831065</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.257942628972061</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.430341514036757</v>
+        <v>-5.78358335338838</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.9757297639653912</v>
+        <v>0.834433028224741</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.257942628972061</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.180700484050805</v>
+        <v>-5.533942323402428</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.075929799847613</v>
+        <v>0.9346330641069631</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.008301598986109</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.926158584709729</v>
+        <v>-5.279400424061352</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.1771133808048</v>
+        <v>1.035816645064151</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.753759699645034</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.69267736248013</v>
+        <v>-5.045919201831754</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.278430298534492</v>
+        <v>1.137133562793842</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.5202784774154354</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.512968832336258</v>
+        <v>-4.866210671687881</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.347421500279082</v>
+        <v>1.206124764538432</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.4631069732527393</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.380693358705371</v>
+        <v>-4.733935198056995</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.395699176478464</v>
+        <v>1.254402440737814</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.3308314996218527</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.190093684032218</v>
+        <v>-4.543335523383842</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.474754107035362</v>
+        <v>1.333457371294712</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.1402318249486998</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.941093885348638</v>
+        <v>-4.294335724700261</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.587260367732453</v>
+        <v>1.445963631991803</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.1402318249486998</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.749714810487698</v>
+        <v>-4.102956649839321</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.53583606807761</v>
+        <v>1.39453933233696</v>
       </c>
       <c r="F1908" t="n">
         <v>0.05114724991224029</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.470687514832071</v>
+        <v>-3.823929354183694</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.695991328216947</v>
+        <v>1.554694592476297</v>
       </c>
       <c r="F1909" t="n">
         <v>0.05114724991224029</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.193949340161259</v>
+        <v>-3.547191179512881</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.810065610071267</v>
+        <v>1.668768874330617</v>
       </c>
       <c r="F1910" t="n">
         <v>0.2329639110221661</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.067056933726189</v>
+        <v>-3.420298773077811</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.852108586391816</v>
+        <v>1.710811850651166</v>
       </c>
       <c r="F1911" t="n">
         <v>0.359856317457236</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.879469425816262</v>
+        <v>-3.232711265167885</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.920182977460694</v>
+        <v>1.778886241720044</v>
       </c>
       <c r="F1912" t="n">
         <v>0.359856317457236</v>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.637321032362404</v>
+        <v>-2.990562871714026</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.031504689223381</v>
+        <v>1.890207953482731</v>
       </c>
       <c r="F1913" t="n">
         <v>0.359856317457236</v>
@@ -45573,10 +45573,10 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.574091660594056</v>
+        <v>-2.927333499945678</v>
       </c>
       <c r="E1914" t="n">
-        <v>2.051328558389915</v>
+        <v>1.910031822649265</v>
       </c>
       <c r="F1914" t="n">
         <v>0.359856317457236</v>
@@ -45596,10 +45596,10 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.387603968217049</v>
+        <v>-2.740845807568672</v>
       </c>
       <c r="E1915" t="n">
-        <v>2.123421729351294</v>
+        <v>1.982124993610644</v>
       </c>
       <c r="F1915" t="n">
         <v>0.5463440098342423</v>
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.786553501696439</v>
+        <v>3.42093947657852</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-2.368050363584751</v>
+        <v>-2.486135104028069</v>
       </c>
       <c r="E1916" t="n">
-        <v>2.138944149441539</v>
+        <v>2.091710253264211</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.5658976144665409</v>
+        <v>0.8010547133748451</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.426059287869111</v>
+        <v>3.567153547214094</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240328.xlsx
+++ b/tame_output/ON/bt/strategyON_20240328.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-69.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.7%</t>
+          <t>-65.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-641.6%</t>
+          <t>-642.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-410.2%</t>
+          <t>-433.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.1%</t>
+          <t>-176.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,32 +1318,32 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-143.9%</t>
+          <t>-167.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-89.3%</t>
+          <t>-103.3%</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240573</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.42093947657852</v>
+        <v>3.420939476578522</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-2.486135104028069</v>
+        <v>-2.719696608665228</v>
       </c>
       <c r="E1916" t="n">
-        <v>2.091710253264211</v>
+        <v>1.998285651409347</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.8010547133748451</v>
+        <v>0.5674932087376856</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.567153547214094</v>
+        <v>3.427016644431798</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240328.xlsx
+++ b/tame_output/ON/bt/strategyON_20240328.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-29.8%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-642.5%</t>
+          <t>-642.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-103.3%</t>
+          <t>-164.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1916"/>
+  <dimension ref="A1:G1917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.420939476578522</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45629,6 +45629,29 @@
       </c>
       <c r="G1916" t="n">
         <v>3.427016644431798</v>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="2" t="n">
+        <v>45379</v>
+      </c>
+      <c r="B1917" t="n">
+        <v>3.414735425947276</v>
+      </c>
+      <c r="C1917" t="n">
+        <v>2.818404837287301</v>
+      </c>
+      <c r="D1917" t="n">
+        <v>-2.719696608665228</v>
+      </c>
+      <c r="E1917" t="n">
+        <v>1.998285651409347</v>
+      </c>
+      <c r="F1917" t="n">
+        <v>0.5674932087376856</v>
+      </c>
+      <c r="G1917" t="n">
+        <v>2.811468634273669</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240328.xlsx
+++ b/tame_output/ON/bt/strategyON_20240328.xlsx
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.81245010338991</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.414735425947276</v>
+        <v>3.414735425947278</v>
       </c>
       <c r="C1917" t="n">
         <v>2.818404837287301</v>

--- a/tame_output/ON/bt/strategyON_20240328.xlsx
+++ b/tame_output/ON/bt/strategyON_20240328.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-3.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.6%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,11 +969,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.7%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-642.3%</t>
+          <t>-642.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-433.5%</t>
+          <t>-441.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1127,11 +1127,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,27 +1170,27 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-60.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.4%</t>
+          <t>-180.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,47 +1308,47 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.2%</t>
+          <t>-148.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.2%</t>
+          <t>-147.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.9%</t>
+          <t>-92.0%</t>
         </is>
       </c>
     </row>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.467635205072789</v>
+        <v>-9.787768293193075</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.625656330891716</v>
+        <v>-0.7537095661398303</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.599709265420042</v>
+        <v>-2.643202616850729</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.601928616199123</v>
+        <v>1.575832605340711</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.415619691103975</v>
+        <v>-9.735752779224262</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6008597896177896</v>
+        <v>-0.7289130248659044</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.599709265420042</v>
+        <v>-2.643202616850729</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.605918951885524</v>
+        <v>1.579822941027111</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.49691162065818</v>
+        <v>-9.817044708778466</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6348517883382132</v>
+        <v>-0.7629050235863279</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.599709265420042</v>
+        <v>-2.643202616850729</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.604443724986782</v>
+        <v>1.57834771412837</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.299642214930183</v>
+        <v>-9.619775303050469</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5408906158821423</v>
+        <v>-0.6689438511302566</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.402439859692044</v>
+        <v>-2.445933211122731</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.737858778588453</v>
+        <v>1.711762767730041</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.100490107693084</v>
+        <v>-9.42062319581337</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4742809066339855</v>
+        <v>-0.6023341418821002</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.23711733374223</v>
+        <v>-2.280610685172917</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.824001160511658</v>
+        <v>1.797905149653246</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.874644954973673</v>
+        <v>-9.19477804309396</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3743637725100126</v>
+        <v>-0.5024170077581274</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.195190658155067</v>
+        <v>-2.238684009585754</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.858736238900165</v>
+        <v>1.832640228041753</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.588370142650978</v>
+        <v>-8.908503230771265</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.258714703024876</v>
+        <v>-0.3867679382729903</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.195190658155067</v>
+        <v>-2.238684009585754</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.859875383456224</v>
+        <v>1.833779372597812</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.361574315577645</v>
+        <v>-8.681707403697931</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.1653625980334348</v>
+        <v>-0.2934158332815495</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.127076713533522</v>
+        <v>-2.170570064964209</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.903377524391258</v>
+        <v>1.877281513532846</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.077665584648896</v>
+        <v>-8.397798672769182</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.04606540142329862</v>
+        <v>-0.1741186366714134</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.127076713533522</v>
+        <v>-2.170570064964209</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.909111228629895</v>
+        <v>1.883015217771483</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.830678334455944</v>
+        <v>-8.150811422576231</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.0429922362600168</v>
+        <v>-0.08506099898809794</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.88008946334057</v>
+        <v>-1.923582814771257</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.047566316351801</v>
+        <v>2.021470305493389</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.566841467251875</v>
+        <v>-7.886974555372162</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.1386435018287369</v>
+        <v>0.01059026658062212</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.88008946334057</v>
+        <v>-1.923582814771257</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.037682835038893</v>
+        <v>2.011586824180481</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.299599666383478</v>
+        <v>-7.619732754503765</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.2437056616767221</v>
+        <v>0.115652426428607</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.88008946334057</v>
+        <v>-1.923582814771257</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.03584827453952</v>
+        <v>2.009752263681107</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.023790502982994</v>
+        <v>-7.343923591103281</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.3537290120634546</v>
+        <v>0.2256757768153399</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.791070155061837</v>
+        <v>-1.834563506492524</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.088959544533298</v>
+        <v>2.062863533674887</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567245</v>
+        <v>3.800825778567243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.754722915216014</v>
+        <v>-7.074856003336301</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.4620245533157403</v>
+        <v>0.3339713180676251</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.522002567294857</v>
+        <v>-1.565495918725544</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.25106860333898</v>
+        <v>2.224972592480568</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.490662976893218</v>
+        <v>-6.810796065013506</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.5543882124831065</v>
+        <v>0.4263349772349914</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.257942628972061</v>
+        <v>-1.301435980402748</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.396244250170906</v>
+        <v>2.370148239312493</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.78358335338838</v>
+        <v>-6.103716441508667</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.834433028224741</v>
+        <v>0.7063797929766258</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.257942628972061</v>
+        <v>-1.301435980402748</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.393457216510605</v>
+        <v>2.367361205652192</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.533942323402428</v>
+        <v>-5.854075411522715</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.9346330641069631</v>
+        <v>0.8065798288588484</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.008301598986109</v>
+        <v>-1.051794950416796</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.543585458390017</v>
+        <v>2.517489447531605</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.279400424061352</v>
+        <v>-5.59953351218164</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.035816645064151</v>
+        <v>0.907763409816035</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.753759699645034</v>
+        <v>-0.797253051075721</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.695677419215419</v>
+        <v>2.669581408357007</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.045919201831754</v>
+        <v>-5.366052289952042</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.137133562793842</v>
+        <v>1.009080327545727</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5202784774154354</v>
+        <v>-0.5637718288461224</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.84369058139103</v>
+        <v>2.817594570532619</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.866210671687881</v>
+        <v>-5.186343759808169</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.206124764538432</v>
+        <v>1.078071529290317</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4631069732527393</v>
+        <v>-0.5066003246834263</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.875101273575689</v>
+        <v>2.849005262717277</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.733935198056995</v>
+        <v>-5.054068286177283</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.254402440737814</v>
+        <v>1.126349205489698</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3308314996218527</v>
+        <v>-0.3743248510525397</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.949834044501248</v>
+        <v>2.923738033642836</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.543335523383842</v>
+        <v>-4.86346861150413</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.333457371294712</v>
+        <v>1.205404136046596</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1402318249486998</v>
+        <v>-0.1837251763793868</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.067008909992777</v>
+        <v>3.040912899134364</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.294335724700261</v>
+        <v>-4.614468812820549</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.445963631991803</v>
+        <v>1.317910396743687</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1402318249486998</v>
+        <v>-0.1837251763793868</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.079915251216435</v>
+        <v>3.053819240358023</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.102956649839321</v>
+        <v>-4.423089737959609</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.39453933233696</v>
+        <v>1.266486097088845</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.05114724991224029</v>
+        <v>0.00765389848155329</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.066766766533781</v>
+        <v>3.040670755675368</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.823929354183694</v>
+        <v>-4.144062442303982</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.554694592476297</v>
+        <v>1.426641357228182</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.05114724991224029</v>
+        <v>0.00765389848155329</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.115311108410867</v>
+        <v>3.089215097552455</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.547191179512881</v>
+        <v>-3.867324267633169</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.668768874330617</v>
+        <v>1.540715639082502</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.2329639110221661</v>
+        <v>0.1894705595914791</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.227780117062817</v>
+        <v>3.201684106204405</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.420298773077811</v>
+        <v>-3.7404318611981</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.710811850651166</v>
+        <v>1.582758615403051</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.359856317457236</v>
+        <v>0.316362966026549</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.295201574670381</v>
+        <v>3.269105563811969</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.232711265167885</v>
+        <v>-3.552844353288173</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.778886241720044</v>
+        <v>1.650833006471929</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.359856317457236</v>
+        <v>0.316362966026549</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.288240962575288</v>
+        <v>3.262144951716876</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.990562871714026</v>
+        <v>-3.310695959834315</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.890207953482731</v>
+        <v>1.762154718234615</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.359856317457236</v>
+        <v>0.316362966026549</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.302703316956431</v>
+        <v>3.276607306098019</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.927333499945678</v>
+        <v>-3.247466588065966</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.910031822649265</v>
+        <v>1.78197858740115</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.359856317457236</v>
+        <v>0.316362966026549</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.297235437415626</v>
+        <v>3.271139426557214</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.740845807568672</v>
+        <v>-3.06097889568896</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.982124993610644</v>
+        <v>1.854071758362529</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.5463440098342423</v>
+        <v>0.5028506584035553</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.406626146852406</v>
+        <v>3.380530135993995</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245010338991</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-2.719696608665228</v>
+        <v>-3.039829696785517</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.998285651409347</v>
+        <v>1.870232416161232</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.5674932087376856</v>
+        <v>0.5239998573069986</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.427016644431798</v>
+        <v>3.400920633573386</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.414735425947278</v>
+        <v>3.425974421473326</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.818404837287301</v>
+        <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-2.719696608665228</v>
+        <v>-2.800094121837921</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.998285651409347</v>
+        <v>1.961907354487321</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.5674932087376856</v>
+        <v>0.7637354322545938</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.811468634273669</v>
+        <v>3.540542686888994</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240328.xlsx
+++ b/tame_output/ON/bt/strategyON_20240328.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-67.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-575.2%</t>
+          <t>-539.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-45.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.2%</t>
+          <t>-61.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-642.7%</t>
+          <t>498.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-441.6%</t>
+          <t>-403.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-230.5%</t>
+          <t>-216.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-35.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-60.6%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-180.0%</t>
+          <t>-164.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,42 +1308,42 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-147.6%</t>
+          <t>-170.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-92.0%</t>
+          <t>-105.8%</t>
         </is>
       </c>
     </row>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.01109035984100631</v>
+        <v>0.3421514795106159</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.121688151287636</v>
+        <v>3.262984887028284</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.09286226026875799</v>
+        <v>0.2603795790828642</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.079062117071773</v>
+        <v>3.220358852812422</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.1600713681406357</v>
+        <v>0.1931704712109866</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.056943790756725</v>
+        <v>3.198240526497373</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.1560799153454455</v>
+        <v>0.1971619240061768</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.056365167994041</v>
+        <v>3.19766190373469</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.5542283462987061</v>
+        <v>-0.2009865069470839</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.8950326871178</v>
+        <v>3.036329422858449</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7758502798568236</v>
+        <v>-0.4226084405052014</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.806250130293475</v>
+        <v>2.947546866034124</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9838543382099009</v>
+        <v>-0.6306124988582786</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.727940651506169</v>
+        <v>2.869237387246818</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.254254300918786</v>
+        <v>-0.901012461567164</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.614862122760603</v>
+        <v>2.756158858501252</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.593412678507308</v>
+        <v>-1.240170839155686</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.472283071031643</v>
+        <v>2.613579806772292</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.921429900234787</v>
+        <v>-1.568188060883165</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.36141447207942</v>
+        <v>2.502711207820068</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.918093153725816</v>
+        <v>-1.564851314374194</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.370847921091577</v>
+        <v>2.512144656832226</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.284804205392361</v>
+        <v>-1.931562366040739</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.225269892468691</v>
+        <v>2.366566628209339</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.669984596322434</v>
+        <v>-2.316742756970812</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.069740274909525</v>
+        <v>2.211037010650174</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.013667369549097</v>
+        <v>-2.660425530197474</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.934036289073476</v>
+        <v>2.075333024814125</v>
       </c>
       <c r="F1856" t="n">
         <v>0.003417817992306726</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.371317719787445</v>
+        <v>-3.018075880435823</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.787082207634395</v>
+        <v>1.928378943375043</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.3542325322460414</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.377978660009592</v>
+        <v>-3.02473682065797</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.786190758245795</v>
+        <v>1.927487493986444</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.3542325322460414</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.80978445315938</v>
+        <v>-3.456542613807758</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.599801328453284</v>
+        <v>1.741098064193933</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4906500286873084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.136216982027124</v>
+        <v>-3.782975142675502</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.457513091908277</v>
+        <v>1.598809827648927</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.5731182791944566</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.137781133137427</v>
+        <v>-3.784539293785805</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.455468023120121</v>
+        <v>1.596764758860771</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.5731182791944566</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.50140737803774</v>
+        <v>-4.148165538686118</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.316505085394237</v>
+        <v>1.457801821134887</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.6713399160615824</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.498980313509022</v>
+        <v>-4.145738474157399</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.316730426211556</v>
+        <v>1.458027161952206</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.671672697868734</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.907569090689701</v>
+        <v>-4.554327251338078</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.152056459354044</v>
+        <v>1.293353195094693</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.080261475049412</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.320551574830795</v>
+        <v>-4.967309735479172</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.9820488981690669</v>
+        <v>1.123345633909716</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.080261475049412</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.736943449117792</v>
+        <v>-5.383701609766169</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8134861990631452</v>
+        <v>0.9547829348037946</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.080261475049412</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.113620459647636</v>
+        <v>-5.760378620296014</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.6730740855198865</v>
+        <v>0.8143708212605358</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.080261475049412</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.127335323972748</v>
+        <v>-5.774093484621125</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.663687704935537</v>
+        <v>0.8049844406761864</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.080261475049412</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.440160123217727</v>
+        <v>-6.086918283866105</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5369627052925461</v>
+        <v>0.6782594410331955</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.080261475049412</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.444973161683064</v>
+        <v>-6.091731322331442</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5388164658356196</v>
+        <v>0.680113201576269</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.081808109752198</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.8783222697933</v>
+        <v>-6.525080430441678</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3614505180571221</v>
+        <v>0.5027472537977715</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.081808109752198</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.261323658535932</v>
+        <v>-6.908081819184309</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2081478612384853</v>
+        <v>0.3494445969791347</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.081808109752198</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.636308984707209</v>
+        <v>-7.283067145355586</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.06072524674140478</v>
+        <v>0.2020219824820542</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.456793435923476</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.99583930721121</v>
+        <v>-7.642597467859588</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.07773657896214559</v>
+        <v>0.0635601567785038</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.456793435923476</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.322239335876223</v>
+        <v>-7.968997496524601</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2003805704709736</v>
+        <v>-0.05908383473032419</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.783193464588488</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.315763189082663</v>
+        <v>-7.962521349731041</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1947483611317806</v>
+        <v>-0.05345162539113124</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.776717317794929</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.312072264126252</v>
+        <v>-7.95883042477463</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1932719911492167</v>
+        <v>-0.05197525540856685</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.776717317794929</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.516330439456116</v>
+        <v>-8.163088600104492</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2694620641625196</v>
+        <v>-0.1281653284218693</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.904356262408918</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.676969465944481</v>
+        <v>-8.323727626592857</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3292351202734296</v>
+        <v>-0.1879383845327793</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.019089735411313</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.603499634277032</v>
+        <v>-8.250257794925409</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.284475486113029</v>
+        <v>-0.1431787503723787</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.945619903743865</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.778624051663575</v>
+        <v>-8.425382212311952</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3399700323201293</v>
+        <v>-0.1986732965794795</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.120744321130409</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.013076145678065</v>
+        <v>-8.659834306326442</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4409700348275214</v>
+        <v>-0.2996732990868711</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.120744321130409</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.300879990215304</v>
+        <v>-8.94763815086368</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5627637634163931</v>
+        <v>-0.4214670276757428</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.408548165667647</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.530704437379129</v>
+        <v>-9.177462598027505</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6535777524433666</v>
+        <v>-0.5122810167027163</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.571195702737807</v>
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.787768293193075</v>
+        <v>-9.409491517763767</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7537095661398303</v>
+        <v>-0.6023988559681066</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.643202616850729</v>
+        <v>-2.633208399926231</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.575832605340711</v>
+        <v>1.581829135495409</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.735752779224262</v>
+        <v>-9.357476003794954</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.7289130248659044</v>
+        <v>-0.5776023146941807</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.643202616850729</v>
+        <v>-2.633208399926231</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.579822941027111</v>
+        <v>1.58581947118181</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.817044708778466</v>
+        <v>-9.438767933349158</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7629050235863279</v>
+        <v>-0.6115943134146038</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.643202616850729</v>
+        <v>-2.633208399926231</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.57834771412837</v>
+        <v>1.584344244283069</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.619775303050469</v>
+        <v>-9.241498527621161</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6689438511302566</v>
+        <v>-0.5176331409585329</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.445933211122731</v>
+        <v>-2.435938994198232</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.711762767730041</v>
+        <v>1.71775929788474</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.42062319581337</v>
+        <v>-9.042346420384062</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6023341418821002</v>
+        <v>-0.4510234317103761</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.280610685172917</v>
+        <v>-2.270616468248419</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.797905149653246</v>
+        <v>1.803901679807945</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.19477804309396</v>
+        <v>-8.816501267664652</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5024170077581274</v>
+        <v>-0.3511062975864037</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.238684009585754</v>
+        <v>-2.228689792661255</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.832640228041753</v>
+        <v>1.838636758196452</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.908503230771265</v>
+        <v>-8.530226455341957</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3867679382729903</v>
+        <v>-0.2354572281012666</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.238684009585754</v>
+        <v>-2.228689792661255</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.833779372597812</v>
+        <v>1.839775902752511</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.681707403697931</v>
+        <v>-8.303430628268623</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2934158332815495</v>
+        <v>-0.1421051231098254</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.170570064964209</v>
+        <v>-2.160575848039711</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.877281513532846</v>
+        <v>1.883278043687545</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.397798672769182</v>
+        <v>-8.019521897339875</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.1741186366714134</v>
+        <v>-0.02280792649968966</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.170570064964209</v>
+        <v>-2.160575848039711</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.883015217771483</v>
+        <v>1.889011747926181</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.150811422576231</v>
+        <v>-7.772534647146922</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.08506099898809794</v>
+        <v>0.06624971118362621</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.923582814771257</v>
+        <v>-1.913588597846759</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.021470305493389</v>
+        <v>2.027466835648087</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.886974555372162</v>
+        <v>-7.508697779942853</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.01059026658062212</v>
+        <v>0.1619009767523463</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.923582814771257</v>
+        <v>-1.913588597846759</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.011586824180481</v>
+        <v>2.01758335433518</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.619732754503765</v>
+        <v>-7.241455979074456</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.115652426428607</v>
+        <v>0.2669631366003311</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.923582814771257</v>
+        <v>-1.913588597846759</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.009752263681107</v>
+        <v>2.015748793835806</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.343923591103281</v>
+        <v>-6.965646815673972</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.2256757768153399</v>
+        <v>0.3769864869870641</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.834563506492524</v>
+        <v>-1.824569289568025</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.062863533674887</v>
+        <v>2.068860063829585</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.074856003336301</v>
+        <v>-6.696579227906993</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.3339713180676251</v>
+        <v>0.4852820282393497</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.565495918725544</v>
+        <v>-1.555501701801046</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.224972592480568</v>
+        <v>2.230969122635266</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.810796065013506</v>
+        <v>-6.432519289584197</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.4263349772349914</v>
+        <v>0.577645687406716</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.301435980402748</v>
+        <v>-1.29144176347825</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.370148239312493</v>
+        <v>2.376144769467192</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.103716441508667</v>
+        <v>-5.725439666079359</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.7063797929766258</v>
+        <v>0.8576905031483504</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.301435980402748</v>
+        <v>-1.29144176347825</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.367361205652192</v>
+        <v>2.373357735806891</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.854075411522715</v>
+        <v>-5.475798636093407</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.8065798288588484</v>
+        <v>0.9578905390305725</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.051794950416796</v>
+        <v>-1.041800733492298</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.517489447531605</v>
+        <v>2.523485977686303</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.59953351218164</v>
+        <v>-5.221256736752331</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.907763409816035</v>
+        <v>1.05907411998776</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.797253051075721</v>
+        <v>-0.7872588341512228</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.669581408357007</v>
+        <v>2.675577938511706</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.366052289952042</v>
+        <v>-4.987775514522732</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.009080327545727</v>
+        <v>1.160391037717452</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5637718288461224</v>
+        <v>-0.5537776119216242</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.817594570532619</v>
+        <v>2.823591100687318</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.186343759808169</v>
+        <v>-4.808066984378859</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.078071529290317</v>
+        <v>1.229382239462042</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5066003246834263</v>
+        <v>-0.4966061077589281</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.849005262717277</v>
+        <v>2.855001792871976</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.054068286177283</v>
+        <v>-4.675791510747973</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.126349205489698</v>
+        <v>1.277659915661423</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3743248510525397</v>
+        <v>-0.3643306341280415</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.923738033642836</v>
+        <v>2.929734563797535</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.86346861150413</v>
+        <v>-4.48519183607482</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.205404136046596</v>
+        <v>1.356714846218321</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1837251763793868</v>
+        <v>-0.1737309594548886</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.040912899134364</v>
+        <v>3.046909429289063</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.614468812820549</v>
+        <v>-4.236192037391239</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.317910396743687</v>
+        <v>1.469221106915412</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1837251763793868</v>
+        <v>-0.1737309594548886</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.053819240358023</v>
+        <v>3.059815770512722</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.423089737959609</v>
+        <v>-4.044812962530299</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.266486097088845</v>
+        <v>1.417796807260569</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.00765389848155329</v>
+        <v>0.01764811540605149</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.040670755675368</v>
+        <v>3.046667285830067</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.144062442303982</v>
+        <v>-3.765785666874672</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.426641357228182</v>
+        <v>1.577952067399907</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.00765389848155329</v>
+        <v>0.01764811540605149</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.089215097552455</v>
+        <v>3.095211627707154</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.867324267633169</v>
+        <v>-3.48904749220386</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.540715639082502</v>
+        <v>1.692026349254226</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.1894705595914791</v>
+        <v>0.1994647765159773</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.201684106204405</v>
+        <v>3.207680636359104</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.7404318611981</v>
+        <v>-3.36215508576879</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.582758615403051</v>
+        <v>1.734069325574776</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.316362966026549</v>
+        <v>0.3263571829510472</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.269105563811969</v>
+        <v>3.275102093966668</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.552844353288173</v>
+        <v>-3.174567577858863</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.650833006471929</v>
+        <v>1.802143716643653</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.316362966026549</v>
+        <v>0.3263571829510472</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.262144951716876</v>
+        <v>3.268141481871575</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.310695959834315</v>
+        <v>-2.932419184405005</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.762154718234615</v>
+        <v>1.91346542840634</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.316362966026549</v>
+        <v>0.3263571829510472</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.276607306098019</v>
+        <v>3.282603836252718</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.247466588065966</v>
+        <v>-2.869189812636657</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.78197858740115</v>
+        <v>1.933289297572874</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.316362966026549</v>
+        <v>0.3263571829510472</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.271139426557214</v>
+        <v>3.277135956711913</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.06097889568896</v>
+        <v>-2.68270212025965</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.854071758362529</v>
+        <v>2.005382468534254</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.5028506584035553</v>
+        <v>0.5128448753280535</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.380530135993995</v>
+        <v>3.386526666148693</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.039829696785517</v>
+        <v>-2.661552921356207</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.870232416161232</v>
+        <v>2.021543126332957</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.5239998573069986</v>
+        <v>0.5339940742314968</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.400920633573386</v>
+        <v>3.406917163728085</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.425974421473326</v>
+        <v>3.425974421473325</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-2.800094121837921</v>
+        <v>-2.422600247359135</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.961907354487321</v>
+        <v>2.112904904278836</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.7637354322545938</v>
+        <v>0.5339940742314968</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.540542686888994</v>
+        <v>3.402697872075136</v>
       </c>
     </row>
   </sheetData>
